--- a/SourceData/kkami_datatable_ver02.xlsx
+++ b/SourceData/kkami_datatable_ver02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1883ECAC-4F72-4A9F-85E0-AD238862DEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{508E8EE2-8B8F-422F-917A-52259FED4984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4470" yWindow="4650" windowWidth="27705" windowHeight="13935" tabRatio="795" firstSheet="7" activeTab="13" xr2:uid="{3796E205-6E29-44DF-89A9-B95A9916162D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="795" activeTab="4" xr2:uid="{3796E205-6E29-44DF-89A9-B95A9916162D}"/>
   </bookViews>
   <sheets>
     <sheet name="version" sheetId="21" r:id="rId1"/>
@@ -1473,23 +1473,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>vfx_boss3_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vfx_boss4_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vfx_boss5_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>vfx_boss3_02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>vfx_boss4_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vfx_boss3_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vfx_boss4_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vfx_boss5_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1673,7 +1673,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1716,32 +1716,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1752,26 +1728,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1783,25 +1765,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1815,7 +1791,43 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2368,20 +2380,20 @@
     </row>
     <row r="3" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="23"/>
+      <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
@@ -2400,24 +2412,24 @@
     </row>
     <row r="9" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="24"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="23"/>
+      <c r="C11" s="15"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="28"/>
-      <c r="C12" s="23"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15"/>
     </row>
     <row r="13" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="24"/>
-      <c r="C13" s="25"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="9" t="s">
@@ -2436,24 +2448,24 @@
     </row>
     <row r="16" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="27"/>
+      <c r="C17" s="22"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="23"/>
+      <c r="C18" s="15"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="28"/>
-      <c r="C19" s="23"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="15"/>
     </row>
     <row r="20" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="24"/>
-      <c r="C20" s="25"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="17"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
@@ -2472,24 +2484,24 @@
     </row>
     <row r="23" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="21"/>
+      <c r="C24" s="24"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="C25" s="23"/>
+      <c r="C25" s="15"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="28"/>
-      <c r="C26" s="23"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="15"/>
     </row>
     <row r="27" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="24"/>
-      <c r="C27" s="25"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
@@ -2508,24 +2520,24 @@
     </row>
     <row r="30" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="27"/>
+      <c r="C31" s="22"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="23"/>
+      <c r="C32" s="15"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B33" s="28"/>
-      <c r="C33" s="23"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="15"/>
     </row>
     <row r="34" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="24"/>
-      <c r="C34" s="25"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="17"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="8" t="s">
@@ -2544,24 +2556,24 @@
     </row>
     <row r="37" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="21"/>
+      <c r="C38" s="24"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="C39" s="23"/>
+      <c r="C39" s="15"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B40" s="28"/>
-      <c r="C40" s="23"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="15"/>
     </row>
     <row r="41" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="24"/>
-      <c r="C41" s="25"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="17"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" s="9" t="s">
@@ -2580,24 +2592,24 @@
     </row>
     <row r="44" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B45" s="26" t="s">
+      <c r="B45" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="27"/>
+      <c r="C45" s="22"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B46" s="22" t="s">
+      <c r="B46" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="C46" s="23"/>
+      <c r="C46" s="15"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B47" s="28"/>
-      <c r="C47" s="23"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
     </row>
     <row r="48" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="24"/>
-      <c r="C48" s="25"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="17"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50" s="8" t="s">
@@ -2616,28 +2628,23 @@
     </row>
     <row r="51" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B52" s="20" t="s">
+      <c r="B52" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="21"/>
+      <c r="C52" s="24"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="C53" s="23"/>
+      <c r="C53" s="15"/>
     </row>
     <row r="54" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="24"/>
-      <c r="C54" s="25"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C13"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B53:C54"/>
     <mergeCell ref="B24:C24"/>
@@ -2649,6 +2656,11 @@
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="B32:C34"/>
     <mergeCell ref="B39:C41"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C13"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3992,20 +4004,20 @@
     </row>
     <row r="3" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="23"/>
+      <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
@@ -4024,137 +4036,137 @@
     </row>
     <row r="9" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="E10" s="26" t="s">
+      <c r="C10" s="24"/>
+      <c r="E10" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="27"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="E11" s="18" t="s">
+      <c r="C11" s="27"/>
+      <c r="E11" s="50" t="s">
         <v>312</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="30" t="s">
         <v>324</v>
       </c>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="39"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="31"/>
     </row>
     <row r="12" spans="2:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
-      <c r="E12" s="18" t="s">
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="E12" s="50" t="s">
         <v>313</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="30" t="s">
         <v>298</v>
       </c>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="31"/>
     </row>
     <row r="13" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="50" t="s">
         <v>314</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="39"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="31"/>
     </row>
     <row r="14" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="50" t="s">
         <v>315</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="39"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="31"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="50" t="s">
         <v>316</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="30" t="s">
         <v>300</v>
       </c>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="39"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="31"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="50" t="s">
         <v>317</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="F16" s="30" t="s">
         <v>302</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="39"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="31"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="50" t="s">
         <v>318</v>
       </c>
-      <c r="F17" s="38" t="s">
+      <c r="F17" s="30" t="s">
         <v>301</v>
       </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="31"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="50" t="s">
         <v>319</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="31"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="50" t="s">
         <v>320</v>
       </c>
-      <c r="F19" s="38" t="s">
+      <c r="F19" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="31"/>
     </row>
     <row r="20" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E20" s="19">
+      <c r="E20" s="51">
         <v>10</v>
       </c>
-      <c r="F20" s="40" t="s">
+      <c r="F20" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="41"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="34"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="9" t="s">
@@ -4173,74 +4185,74 @@
     </row>
     <row r="23" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="27"/>
-      <c r="E24" s="20" t="s">
+      <c r="C24" s="22"/>
+      <c r="E24" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="21"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="24"/>
     </row>
     <row r="25" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="C25" s="33"/>
+      <c r="C25" s="27"/>
       <c r="E25" s="10">
         <v>1</v>
       </c>
-      <c r="F25" s="38" t="s">
+      <c r="F25" s="47" t="s">
         <v>308</v>
       </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="39"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="31"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="22"/>
-      <c r="C26" s="33"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="27"/>
       <c r="E26" s="10">
         <v>2</v>
       </c>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="47" t="s">
         <v>309</v>
       </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="39"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="31"/>
     </row>
     <row r="27" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="22"/>
-      <c r="C27" s="33"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="27"/>
       <c r="E27" s="12">
         <v>3</v>
       </c>
-      <c r="F27" s="40" t="s">
+      <c r="F27" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="41"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="34"/>
     </row>
     <row r="28" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="34"/>
-      <c r="C28" s="35"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E29" s="11"/>
+      <c r="E29" s="45"/>
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
+      <c r="I29" s="46"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="s">
@@ -4259,39 +4271,39 @@
     </row>
     <row r="31" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="21"/>
-      <c r="E32" s="26" t="s">
+      <c r="C32" s="24"/>
+      <c r="E32" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="27"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="33" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="E33" s="22" t="s">
+      <c r="C33" s="27"/>
+      <c r="E33" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="33"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="27"/>
     </row>
     <row r="34" spans="2:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="34"/>
-      <c r="C34" s="35"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="35"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="29"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="29"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="9" t="s">
@@ -4310,24 +4322,24 @@
     </row>
     <row r="37" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B38" s="26" t="s">
+      <c r="B38" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="27"/>
+      <c r="C38" s="22"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="C39" s="23"/>
+      <c r="C39" s="15"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B40" s="28"/>
-      <c r="C40" s="23"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="15"/>
     </row>
     <row r="41" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="24"/>
-      <c r="C41" s="25"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="17"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" s="8" t="s">
@@ -4346,24 +4358,24 @@
     </row>
     <row r="44" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="21"/>
+      <c r="C45" s="24"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B46" s="22" t="s">
+      <c r="B46" s="26" t="s">
         <v>329</v>
       </c>
-      <c r="C46" s="23"/>
+      <c r="C46" s="15"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B47" s="28"/>
-      <c r="C47" s="23"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
     </row>
     <row r="48" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="24"/>
-      <c r="C48" s="25"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="17"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50" s="9" t="s">
@@ -4382,24 +4394,24 @@
     </row>
     <row r="51" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B52" s="26" t="s">
+      <c r="B52" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="27"/>
+      <c r="C52" s="22"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="26" t="s">
         <v>330</v>
       </c>
-      <c r="C53" s="23"/>
+      <c r="C53" s="15"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B54" s="28"/>
-      <c r="C54" s="23"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="15"/>
     </row>
     <row r="55" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="24"/>
-      <c r="C55" s="25"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="17"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57" s="8" t="s">
@@ -4418,24 +4430,24 @@
     </row>
     <row r="58" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B59" s="20" t="s">
+      <c r="B59" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C59" s="21"/>
+      <c r="C59" s="24"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B60" s="22" t="s">
+      <c r="B60" s="26" t="s">
         <v>331</v>
       </c>
-      <c r="C60" s="23"/>
+      <c r="C60" s="15"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B61" s="28"/>
-      <c r="C61" s="23"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="15"/>
     </row>
     <row r="62" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="24"/>
-      <c r="C62" s="25"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="17"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B64" s="9" t="s">
@@ -4454,24 +4466,24 @@
     </row>
     <row r="65" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B66" s="26" t="s">
+      <c r="B66" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C66" s="27"/>
+      <c r="C66" s="22"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="26" t="s">
         <v>332</v>
       </c>
-      <c r="C67" s="23"/>
+      <c r="C67" s="15"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B68" s="28"/>
-      <c r="C68" s="23"/>
+      <c r="B68" s="14"/>
+      <c r="C68" s="15"/>
     </row>
     <row r="69" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="24"/>
-      <c r="C69" s="25"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="17"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" s="8" t="s">
@@ -4490,24 +4502,24 @@
     </row>
     <row r="72" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B73" s="20" t="s">
+      <c r="B73" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="21"/>
+      <c r="C73" s="24"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="C74" s="23"/>
+      <c r="C74" s="15"/>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B75" s="28"/>
-      <c r="C75" s="23"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="15"/>
     </row>
     <row r="76" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="24"/>
-      <c r="C76" s="25"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="17"/>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" s="9" t="s">
@@ -4526,24 +4538,24 @@
     </row>
     <row r="79" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B80" s="26" t="s">
+      <c r="B80" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C80" s="27"/>
+      <c r="C80" s="22"/>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B81" s="22" t="s">
+      <c r="B81" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="C81" s="23"/>
+      <c r="C81" s="15"/>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B82" s="28"/>
-      <c r="C82" s="23"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="15"/>
     </row>
     <row r="83" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="24"/>
-      <c r="C83" s="25"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="17"/>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="8" t="s">
@@ -4562,24 +4574,24 @@
     </row>
     <row r="86" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B87" s="20" t="s">
+      <c r="B87" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C87" s="21"/>
+      <c r="C87" s="24"/>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B88" s="22" t="s">
+      <c r="B88" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="C88" s="23"/>
+      <c r="C88" s="15"/>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B89" s="28"/>
-      <c r="C89" s="23"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="15"/>
     </row>
     <row r="90" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="24"/>
-      <c r="C90" s="25"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="17"/>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92" s="9" t="s">
@@ -4598,54 +4610,27 @@
     </row>
     <row r="93" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B94" s="26" t="s">
+      <c r="B94" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C94" s="27"/>
+      <c r="C94" s="22"/>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B95" s="22" t="s">
+      <c r="B95" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="C95" s="23"/>
+      <c r="C95" s="15"/>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B96" s="28"/>
-      <c r="C96" s="23"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="15"/>
     </row>
     <row r="97" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="24"/>
-      <c r="C97" s="25"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C62"/>
-    <mergeCell ref="E33:I34"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="E32:I32"/>
-    <mergeCell ref="B33:C34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="E24:I24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="B25:C28"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C41"/>
     <mergeCell ref="B45:C45"/>
@@ -4662,6 +4647,33 @@
     <mergeCell ref="B46:C48"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B53:C55"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C62"/>
+    <mergeCell ref="E33:I34"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="E32:I32"/>
+    <mergeCell ref="B33:C34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="B25:C28"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="B5:C6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4825,7 +4837,7 @@
       <c r="A4" s="1">
         <v>50001</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="49" t="s">
         <v>312</v>
       </c>
       <c r="C4" s="1">
@@ -4853,7 +4865,7 @@
       <c r="A5" s="1">
         <v>50002</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="49" t="s">
         <v>312</v>
       </c>
       <c r="C5" s="1">
@@ -4881,7 +4893,7 @@
       <c r="A6" s="1">
         <v>50003</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="49" t="s">
         <v>312</v>
       </c>
       <c r="C6" s="1">
@@ -4909,7 +4921,7 @@
       <c r="A7" s="1">
         <v>50004</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="44" t="s">
         <v>313</v>
       </c>
       <c r="C7" s="1">
@@ -4937,7 +4949,7 @@
       <c r="A8" s="1">
         <v>50005</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="44" t="s">
         <v>313</v>
       </c>
       <c r="C8" s="1">
@@ -4965,7 +4977,7 @@
       <c r="A9" s="1">
         <v>50006</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="44" t="s">
         <v>313</v>
       </c>
       <c r="C9" s="1">
@@ -4993,7 +5005,7 @@
       <c r="A10" s="1">
         <v>50007</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="44" t="s">
         <v>314</v>
       </c>
       <c r="C10" s="1">
@@ -5021,7 +5033,7 @@
       <c r="A11" s="1">
         <v>50008</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="44" t="s">
         <v>314</v>
       </c>
       <c r="C11" s="1">
@@ -5049,7 +5061,7 @@
       <c r="A12" s="1">
         <v>50009</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="44" t="s">
         <v>314</v>
       </c>
       <c r="C12" s="1">
@@ -5077,7 +5089,7 @@
       <c r="A13" s="1">
         <v>50010</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="44" t="s">
         <v>315</v>
       </c>
       <c r="C13" s="1">
@@ -5105,7 +5117,7 @@
       <c r="A14" s="1">
         <v>50011</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="44" t="s">
         <v>315</v>
       </c>
       <c r="C14" s="1">
@@ -5133,7 +5145,7 @@
       <c r="A15" s="1">
         <v>50012</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="44" t="s">
         <v>315</v>
       </c>
       <c r="C15" s="1">
@@ -5161,7 +5173,7 @@
       <c r="A16" s="1">
         <v>50013</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="44" t="s">
         <v>316</v>
       </c>
       <c r="C16" s="1">
@@ -5191,7 +5203,7 @@
       <c r="A17" s="1">
         <v>50014</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="44" t="s">
         <v>316</v>
       </c>
       <c r="C17" s="1">
@@ -5221,7 +5233,7 @@
       <c r="A18" s="1">
         <v>50015</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="44" t="s">
         <v>316</v>
       </c>
       <c r="C18" s="1">
@@ -5251,7 +5263,7 @@
       <c r="A19" s="1">
         <v>50016</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="44" t="s">
         <v>317</v>
       </c>
       <c r="C19" s="1">
@@ -5281,7 +5293,7 @@
       <c r="A20" s="1">
         <v>50017</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="44" t="s">
         <v>318</v>
       </c>
       <c r="C20" s="1">
@@ -5309,7 +5321,7 @@
       <c r="A21" s="1">
         <v>50018</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="44" t="s">
         <v>318</v>
       </c>
       <c r="C21" s="1">
@@ -5337,7 +5349,7 @@
       <c r="A22" s="1">
         <v>50019</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="44" t="s">
         <v>318</v>
       </c>
       <c r="C22" s="1">
@@ -5365,7 +5377,7 @@
       <c r="A23" s="1">
         <v>50020</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="44" t="s">
         <v>319</v>
       </c>
       <c r="C23" s="1">
@@ -5393,7 +5405,7 @@
       <c r="A24" s="1">
         <v>50021</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="44" t="s">
         <v>319</v>
       </c>
       <c r="C24" s="1">
@@ -5421,7 +5433,7 @@
       <c r="A25" s="1">
         <v>50022</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="44" t="s">
         <v>319</v>
       </c>
       <c r="C25" s="1">
@@ -5449,7 +5461,7 @@
       <c r="A26" s="1">
         <v>50023</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="44" t="s">
         <v>320</v>
       </c>
       <c r="C26" s="1">
@@ -5477,7 +5489,7 @@
       <c r="A27" s="1">
         <v>50024</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="44" t="s">
         <v>320</v>
       </c>
       <c r="C27" s="1">
@@ -5505,7 +5517,7 @@
       <c r="A28" s="1">
         <v>50025</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="44" t="s">
         <v>320</v>
       </c>
       <c r="C28" s="1">
@@ -5533,7 +5545,7 @@
       <c r="A29" s="1">
         <v>50026</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="44" t="s">
         <v>321</v>
       </c>
       <c r="C29" s="1">
@@ -5563,7 +5575,7 @@
       <c r="A30" s="1">
         <v>50027</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="44" t="s">
         <v>321</v>
       </c>
       <c r="C30" s="1">
@@ -5593,7 +5605,7 @@
       <c r="A31" s="1">
         <v>50028</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="44" t="s">
         <v>321</v>
       </c>
       <c r="C31" s="1">
@@ -5656,20 +5668,20 @@
     </row>
     <row r="3" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="C5" s="44"/>
+      <c r="C5" s="36"/>
     </row>
     <row r="6" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="45"/>
-      <c r="C6" s="46"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="38"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
@@ -5688,20 +5700,20 @@
     </row>
     <row r="9" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="24"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="C11" s="23"/>
+      <c r="C11" s="15"/>
     </row>
     <row r="12" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="9" t="s">
@@ -5720,20 +5732,20 @@
     </row>
     <row r="15" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="27"/>
+      <c r="C16" s="22"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="C17" s="23"/>
+      <c r="C17" s="15"/>
     </row>
     <row r="18" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
@@ -5752,20 +5764,20 @@
     </row>
     <row r="21" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="21"/>
+      <c r="C22" s="24"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="C23" s="23"/>
+      <c r="C23" s="15"/>
     </row>
     <row r="24" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="24"/>
-      <c r="C24" s="25"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="17"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="9" t="s">
@@ -5784,33 +5796,33 @@
     </row>
     <row r="27" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="27"/>
+      <c r="C28" s="22"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="C29" s="23"/>
+      <c r="C29" s="15"/>
     </row>
     <row r="30" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="24"/>
-      <c r="C30" s="25"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C24"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C30"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C12"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C18"/>
     <mergeCell ref="B5:C6"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C24"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C30"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6195,28 +6207,28 @@
     </row>
     <row r="3" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="E4" s="20" t="s">
+      <c r="C4" s="22"/>
+      <c r="E4" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="24"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="23"/>
+      <c r="C5" s="36"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="15"/>
       <c r="M5">
         <v>1</v>
       </c>
@@ -6231,13 +6243,13 @@
       </c>
     </row>
     <row r="6" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="45"/>
-      <c r="C6" s="46"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="23"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="38"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="15"/>
       <c r="O6" t="s">
         <v>52</v>
       </c>
@@ -6246,11 +6258,11 @@
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="E7" s="14"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="23"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="15"/>
       <c r="M7">
         <v>2</v>
       </c>
@@ -6265,11 +6277,11 @@
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="E8" s="14"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="23"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="15"/>
       <c r="O8" t="s">
         <v>11</v>
       </c>
@@ -6278,11 +6290,11 @@
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="E9" s="14"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="23"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="15"/>
       <c r="O9" t="s">
         <v>54</v>
       </c>
@@ -6291,11 +6303,11 @@
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="E10" s="14"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="23"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="15"/>
       <c r="O10" t="s">
         <v>13</v>
       </c>
@@ -6304,11 +6316,11 @@
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="E11" s="14"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="23"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="15"/>
       <c r="O11" t="s">
         <v>211</v>
       </c>
@@ -6317,11 +6329,11 @@
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="E12" s="14"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="23"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="15"/>
       <c r="M12">
         <v>3</v>
       </c>
@@ -6336,11 +6348,11 @@
       </c>
     </row>
     <row r="13" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E13" s="15"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="25"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="17"/>
       <c r="O13" t="s">
         <v>5</v>
       </c>
@@ -6386,10 +6398,10 @@
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="21"/>
+      <c r="C17" s="24"/>
       <c r="O17" t="s">
         <v>8</v>
       </c>
@@ -6398,10 +6410,10 @@
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="23"/>
+      <c r="C18" s="15"/>
       <c r="M18">
         <v>4</v>
       </c>
@@ -6416,8 +6428,8 @@
       </c>
     </row>
     <row r="19" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
       <c r="O19" t="s">
         <v>215</v>
       </c>
@@ -6536,20 +6548,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C19"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I8"/>
     <mergeCell ref="F9:I9"/>
     <mergeCell ref="F10:I10"/>
     <mergeCell ref="F11:I11"/>
     <mergeCell ref="F12:I12"/>
     <mergeCell ref="F13:I13"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7160,16 +7172,16 @@
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="44"/>
+      <c r="C5" s="36"/>
       <c r="N5">
         <v>1</v>
       </c>
@@ -7184,8 +7196,8 @@
       </c>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="45"/>
-      <c r="C6" s="46"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="38"/>
       <c r="P6" t="s">
         <v>52</v>
       </c>
@@ -7237,10 +7249,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="24"/>
       <c r="P10" t="s">
         <v>13</v>
       </c>
@@ -7249,10 +7261,10 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="C11" s="23"/>
+      <c r="C11" s="15"/>
       <c r="P11" t="s">
         <v>211</v>
       </c>
@@ -7261,8 +7273,8 @@
       </c>
     </row>
     <row r="12" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
       <c r="N12">
         <v>3</v>
       </c>
@@ -7781,20 +7793,20 @@
     </row>
     <row r="3" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C5" s="23"/>
+      <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
@@ -7813,20 +7825,20 @@
     </row>
     <row r="9" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="24"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="23"/>
+      <c r="C11" s="15"/>
     </row>
     <row r="12" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="9" t="s">
@@ -7845,20 +7857,20 @@
     </row>
     <row r="15" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="27"/>
+      <c r="C16" s="22"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="C17" s="23"/>
+      <c r="C17" s="15"/>
     </row>
     <row r="18" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
@@ -7877,20 +7889,20 @@
     </row>
     <row r="21" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="21"/>
+      <c r="C22" s="24"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="C23" s="23"/>
+      <c r="C23" s="15"/>
     </row>
     <row r="24" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="24"/>
-      <c r="C24" s="25"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="17"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="9" t="s">
@@ -7909,20 +7921,20 @@
     </row>
     <row r="27" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="27"/>
+      <c r="C28" s="22"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="C29" s="23"/>
+      <c r="C29" s="15"/>
     </row>
     <row r="30" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="24"/>
-      <c r="C30" s="25"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
@@ -7941,20 +7953,20 @@
     </row>
     <row r="33" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="21"/>
+      <c r="C34" s="24"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="23"/>
+      <c r="C35" s="15"/>
     </row>
     <row r="36" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="17"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
@@ -7978,33 +7990,33 @@
     </row>
     <row r="39" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="27"/>
-      <c r="E40" s="20" t="s">
+      <c r="C40" s="22"/>
+      <c r="E40" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="F40" s="32"/>
-      <c r="G40" s="21"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="24"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C41" s="23"/>
-      <c r="E41" s="28" t="s">
+      <c r="C41" s="15"/>
+      <c r="E41" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="F41" s="29"/>
-      <c r="G41" s="23"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="15"/>
     </row>
     <row r="42" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="24"/>
-      <c r="C42" s="25"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="25"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="17"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="17"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="8" t="s">
@@ -8023,33 +8035,33 @@
     </row>
     <row r="45" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="21"/>
-      <c r="E46" s="26" t="s">
+      <c r="C46" s="24"/>
+      <c r="E46" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F46" s="31"/>
-      <c r="G46" s="27"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="22"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C47" s="23"/>
-      <c r="E47" s="28" t="s">
+      <c r="C47" s="15"/>
+      <c r="E47" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="F47" s="29"/>
-      <c r="G47" s="23"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="15"/>
     </row>
     <row r="48" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="24"/>
-      <c r="C48" s="25"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="25"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="17"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="17"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50" s="9" t="s">
@@ -8068,30 +8080,23 @@
     </row>
     <row r="51" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B52" s="20" t="s">
+      <c r="B52" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="21"/>
+      <c r="C52" s="24"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="C53" s="23"/>
+      <c r="C53" s="15"/>
     </row>
     <row r="54" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="24"/>
-      <c r="C54" s="25"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="B47:C48"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B53:C54"/>
     <mergeCell ref="B4:C4"/>
@@ -8106,7 +8111,14 @@
     <mergeCell ref="B29:C30"/>
     <mergeCell ref="B35:C36"/>
     <mergeCell ref="B41:C42"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="B47:C48"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B40:C40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8141,16 +8153,16 @@
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="40" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="44"/>
+      <c r="C5" s="36"/>
       <c r="N5">
         <v>1</v>
       </c>
@@ -8165,8 +8177,8 @@
       </c>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="45"/>
-      <c r="C6" s="46"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="38"/>
       <c r="P6" t="s">
         <v>52</v>
       </c>
@@ -8218,10 +8230,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="24"/>
       <c r="P10" t="s">
         <v>13</v>
       </c>
@@ -8230,10 +8242,10 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="C11" s="23"/>
+      <c r="C11" s="15"/>
       <c r="P11" t="s">
         <v>211</v>
       </c>
@@ -8242,8 +8254,8 @@
       </c>
     </row>
     <row r="12" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
       <c r="N12">
         <v>3</v>
       </c>
@@ -8873,7 +8885,7 @@
       <c r="H4" s="1">
         <v>1</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="44" t="s">
         <v>305</v>
       </c>
     </row>
@@ -8900,7 +8912,7 @@
       <c r="H5" s="1">
         <v>1.5</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="44" t="s">
         <v>306</v>
       </c>
     </row>
@@ -9198,20 +9210,20 @@
     </row>
     <row r="3" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="23"/>
+      <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
@@ -9230,20 +9242,20 @@
     </row>
     <row r="9" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="24"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="23"/>
+      <c r="C11" s="15"/>
     </row>
     <row r="12" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="9" t="s">
@@ -9262,24 +9274,24 @@
     </row>
     <row r="15" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="27"/>
+      <c r="C16" s="22"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C17" s="23"/>
+      <c r="C17" s="15"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="28"/>
-      <c r="C18" s="23"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
     </row>
     <row r="19" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
@@ -9298,20 +9310,20 @@
     </row>
     <row r="22" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="21"/>
+      <c r="C23" s="24"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="23"/>
+      <c r="C24" s="15"/>
     </row>
     <row r="25" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="24"/>
-      <c r="C25" s="25"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="17"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="9" t="s">
@@ -9330,24 +9342,24 @@
     </row>
     <row r="28" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="27"/>
+      <c r="C29" s="22"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="23"/>
+      <c r="C30" s="15"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B31" s="28"/>
-      <c r="C31" s="23"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="15"/>
     </row>
     <row r="32" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="24"/>
-      <c r="C32" s="25"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="17"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
@@ -9366,20 +9378,20 @@
     </row>
     <row r="35" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="21"/>
+      <c r="C36" s="24"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="C37" s="23"/>
+      <c r="C37" s="15"/>
     </row>
     <row r="38" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="24"/>
-      <c r="C38" s="25"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="17"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="9" t="s">
@@ -9398,20 +9410,20 @@
     </row>
     <row r="41" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="42" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="27"/>
+      <c r="C42" s="22"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="C43" s="23"/>
+      <c r="C43" s="15"/>
     </row>
     <row r="44" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="24"/>
-      <c r="C44" s="25"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="17"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46" s="8" t="s">
@@ -9430,20 +9442,20 @@
     </row>
     <row r="47" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="21"/>
+      <c r="C48" s="24"/>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="C49" s="23"/>
+      <c r="C49" s="15"/>
     </row>
     <row r="50" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="24"/>
-      <c r="C50" s="25"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -9705,20 +9717,20 @@
     </row>
     <row r="3" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="23"/>
+      <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
@@ -9737,20 +9749,20 @@
     </row>
     <row r="9" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="24"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="23"/>
+      <c r="C11" s="15"/>
     </row>
     <row r="12" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="9" t="s">
@@ -9767,20 +9779,20 @@
     </row>
     <row r="15" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="27"/>
+      <c r="C16" s="22"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="C17" s="33"/>
+      <c r="C17" s="27"/>
     </row>
     <row r="18" spans="2:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -9913,7 +9925,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEF9670-E1C1-4A3E-A93D-ABC836094F6D}">
-  <dimension ref="A1:J50"/>
+  <dimension ref="B1:J50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.375" customWidth="1"/>
@@ -9921,12 +9933,8 @@
     <col min="3" max="3" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>91</v>
       </c>
@@ -9941,24 +9949,24 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="26" t="s">
+    <row r="3" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="27"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="28" t="s">
+      <c r="C4" s="22"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="23"/>
-    </row>
-    <row r="6" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="15"/>
+    </row>
+    <row r="6" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>93</v>
       </c>
@@ -9973,24 +9981,24 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+    <row r="9" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="21"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="28" t="s">
+      <c r="C10" s="24"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C11" s="23"/>
-    </row>
-    <row r="12" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="15"/>
+    </row>
+    <row r="12" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="9" t="s">
         <v>30</v>
       </c>
@@ -10005,26 +10013,26 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="26" t="s">
+    <row r="15" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="27"/>
+      <c r="C16" s="22"/>
     </row>
     <row r="17" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="C17" s="33"/>
+      <c r="C17" s="27"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="22"/>
-      <c r="C18" s="33"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="27"/>
     </row>
     <row r="19" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
@@ -10047,24 +10055,24 @@
     </row>
     <row r="22" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="21"/>
+      <c r="C23" s="24"/>
     </row>
     <row r="24" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="33"/>
+      <c r="C24" s="27"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="22"/>
-      <c r="C25" s="33"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="27"/>
     </row>
     <row r="26" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="34"/>
-      <c r="C26" s="35"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="29"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="9" t="s">
@@ -10083,20 +10091,20 @@
     </row>
     <row r="29" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="27"/>
+      <c r="C30" s="22"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="23"/>
+      <c r="C31" s="15"/>
     </row>
     <row r="32" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="24"/>
-      <c r="C32" s="25"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="17"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="8" t="s">
@@ -10115,20 +10123,20 @@
     </row>
     <row r="35" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="21"/>
+      <c r="C36" s="24"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="C37" s="23"/>
+      <c r="C37" s="15"/>
     </row>
     <row r="38" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="24"/>
-      <c r="C38" s="25"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="17"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="9" t="s">
@@ -10147,20 +10155,20 @@
     </row>
     <row r="41" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="42" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="27"/>
+      <c r="C42" s="22"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C43" s="23"/>
+      <c r="C43" s="15"/>
     </row>
     <row r="44" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="24"/>
-      <c r="C44" s="25"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="17"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46" s="8" t="s">
@@ -10179,23 +10187,28 @@
     </row>
     <row r="47" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="21"/>
+      <c r="C48" s="24"/>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C49" s="23"/>
+      <c r="C49" s="15"/>
     </row>
     <row r="50" spans="2:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="24"/>
-      <c r="C50" s="25"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B49:C50"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B24:C26"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B16:C16"/>
@@ -10207,11 +10220,6 @@
     <mergeCell ref="B11:C12"/>
     <mergeCell ref="B31:C32"/>
     <mergeCell ref="B37:C38"/>
-    <mergeCell ref="B49:C50"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B24:C26"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10374,10 +10382,10 @@
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -10398,10 +10406,10 @@
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -10422,7 +10430,7 @@
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>356</v>
